--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/antofagasta.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>21374.43</v>
+        <v>21264.61</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>23235.46</v>
+        <v>23003.57</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4381.76</v>
+        <v>4357.81</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>31365.72</v>
+        <v>31016.26</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>122.26</v>
+        <v>122.66</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5087.69</v>
+        <v>5066.72</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>20305.71</v>
+        <v>20222.02</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>752.38</v>
+        <v>757.6900000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>32846.63</v>
+        <v>33078.45</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>39893.94</v>
+        <v>39750.89</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>15032.82</v>
+        <v>14978.91</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6112.45</v>
+        <v>6099.22</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>987.16</v>
+        <v>985.02</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>30024.9</v>
+        <v>29959.92</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8049.88</v>
+        <v>8016.13</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>440.1</v>
+        <v>438.25</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2979.82</v>
+        <v>2945.33</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>16368.76</v>
+        <v>16179.32</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>62032.41</v>
+        <v>61982.55</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3578.46</v>
+        <v>3587.95</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1810.49</v>
+        <v>1807.95</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>52453.27</v>
+        <v>52379.69</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4366.03</v>
+        <v>4403.35</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>9940.43</v>
+        <v>10025.38</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>12443.2</v>
+        <v>12603.09</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>163.48</v>
+        <v>165.58</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>34604.27</v>
+        <v>35048.92</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>31677.12</v>
+        <v>30936.08</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>52466.63</v>
+        <v>52363.31</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3836.69</v>
+        <v>3929.99</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>20419.34</v>
+        <v>21026.27</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>31821.93</v>
+        <v>32767.77</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5561.3</v>
+        <v>5519.68</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>31713.01</v>
+        <v>31579.3</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>19837.13</v>
+        <v>19939.83</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1361.05</v>
+        <v>1362.36</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>36669.63</v>
+        <v>36704.97</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>32728.39</v>
+        <v>32808.91</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2901.44</v>
+        <v>2864.09</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>60446.66</v>
+        <v>60020.08</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1705.69</v>
+        <v>1705.61</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>45328.15</v>
+        <v>45367.2</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>36372.19</v>
+        <v>35845.99</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>18793.41</v>
+        <v>18389.07</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8243.68</v>
+        <v>8051.86</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3369.02</v>
+        <v>3280.31</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>34461.83</v>
+        <v>34562.15</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>8976.99</v>
+        <v>9014.299999999999</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>46500.35</v>
+        <v>47072.65</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1396.61</v>
+        <v>1413.8</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>222.75</v>
+        <v>225.65</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>58944.5</v>
+        <v>59066.6</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>35134.43</v>
+        <v>35207.21</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>22218.85</v>
+        <v>22264.88</v>
       </c>
     </row>
     <row r="56">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>49029.09</v>
+        <v>48610.9</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>32743.38</v>
+        <v>33109.57</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>601.58</v>
+        <v>607.29</v>
       </c>
     </row>
     <row r="59">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>294.11</v>
+        <v>295.55</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>61940.01</v>
+        <v>62269.37</v>
       </c>
     </row>
     <row r="61">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>13758.33</v>
+        <v>13831.49</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>36916.5</v>
+        <v>37112.8</v>
       </c>
     </row>
     <row r="63">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>36110.38</v>
+        <v>35836.44</v>
       </c>
     </row>
     <row r="64">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>17895.31</v>
+        <v>18065.3</v>
       </c>
     </row>
     <row r="65">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>57937.66</v>
+        <v>58517.82</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>37578.56</v>
+        <v>37388.2</v>
       </c>
     </row>
     <row r="67">
@@ -4538,13 +4538,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3286.89</v>
+        <v>3279.74</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1410-645-CM26</t>
+          <t>1410-646-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>161.12</v>
+        <v>342.98</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1410-646-CM26</t>
+          <t>1410-645-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>343.73</v>
+        <v>160.77</v>
       </c>
     </row>
     <row r="70">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>586.49</v>
+        <v>583.09</v>
       </c>
     </row>
     <row r="71">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3523.21</v>
+        <v>3482.21</v>
       </c>
     </row>
     <row r="72">
@@ -4843,13 +4843,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>12109.98</v>
+        <v>11969.07</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4291-1122-CM26</t>
+          <t>1079454-324-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4904,13 +4904,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>8056.11</v>
+        <v>58636.91</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1079454-324-CM26</t>
+          <t>1057385-228-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4965,13 +4965,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>58926.64</v>
+        <v>18854.82</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1057385-228-CM26</t>
+          <t>4291-1122-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>18947.98</v>
+        <v>8016.5</v>
       </c>
     </row>
     <row r="76">
@@ -5087,7 +5087,68 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>353.09</v>
+        <v>355.46</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2429-996-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>32373.85</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/antofagasta.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1013609-152-CM25</t>
+          <t>1077908-60-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.158.175-3</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. Campo Militar "Antofagasta"</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>21264.61</v>
+        <v>33090.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>778989-188-CM25</t>
+          <t>769-4403-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>23003.57</v>
+        <v>69127.03999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4291-2327-CM25</t>
+          <t>1077908-82-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4357.81</v>
+        <v>32395.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057384-788-CM25</t>
+          <t>778998-126-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>31016.26</v>
+        <v>3970.31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3858-513-CM25</t>
+          <t>1057385-267-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>122.66</v>
+        <v>20304.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>778992-348-CM25</t>
+          <t>769-4666-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5066.72</v>
+        <v>71149.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1057385-515-CM25</t>
+          <t>1410-735-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>20222.02</v>
+        <v>228.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>697036-126-CM25</t>
+          <t>1057385-313-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>757.6900000000001</v>
+        <v>19585.81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1077908-325-CM25</t>
+          <t>1057384-559-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>33078.45</v>
+        <v>26262.06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1079454-696-CM25</t>
+          <t>1077908-231-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>39750.89</v>
+        <v>32631.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>778992-359-CM25</t>
+          <t>769-4767-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>14978.91</v>
+        <v>70445.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>778998-192-CM25</t>
+          <t>769-4844-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6099.22</v>
+        <v>70741.96000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4291-2855-CM25</t>
+          <t>778992-318-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>985.02</v>
+        <v>3087.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1057384-882-CM25</t>
+          <t>1013609-152-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>65.158.175-3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>Jefatura Adm. y Log. Campo Militar "Antofagasta"</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>29959.92</v>
+        <v>21264.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3391-934-CM25</t>
+          <t>778989-188-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>3a Briagada Acorazada "La Concepción"</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8016.13</v>
+        <v>23003.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>707415-189-CM25</t>
+          <t>4291-2327-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>438.25</v>
+        <v>4357.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>909389-30-CM25</t>
+          <t>1057384-788-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.980.580-1</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Comité de Des Productivo Regional Antofagasta</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2945.33</v>
+        <v>31016.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>778989-201-CM25</t>
+          <t>3858-513-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>16179.32</v>
+        <v>122.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>909389-31-SE25</t>
+          <t>778992-348-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.980.580-1</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Comité de Des Productivo Regional Antofagasta</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1660,24 +1660,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>61982.55</v>
+        <v>5066.72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3506-940-CM25</t>
+          <t>1057385-515-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1687,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1732,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3587.95</v>
+        <v>20222.02</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1079454-697-CM25</t>
+          <t>697036-126-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1763,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1793,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1807.95</v>
+        <v>757.6900000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1079454-702-CM25</t>
+          <t>1077908-325-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1854,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>52379.69</v>
+        <v>33078.45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>778992-376-CM25</t>
+          <t>778992-359-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1875,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1915,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4403.35</v>
+        <v>14978.91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1383364-12-CM25</t>
+          <t>1079454-696-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1936,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1946,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.606.210-7</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Servicio Salud Antof</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1976,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>10025.38</v>
+        <v>39750.89</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057385-570-CM25</t>
+          <t>4291-2855-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1997,22 +1993,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2037,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>12603.09</v>
+        <v>985.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1410-2656-CM25</t>
+          <t>1057384-882-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2058,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2068,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2098,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>165.58</v>
+        <v>29959.92</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1077908-347-CM25</t>
+          <t>778998-192-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2119,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2129,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2159,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>35048.92</v>
+        <v>6099.22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057384-4-CM26</t>
+          <t>3391-934-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>30936.08</v>
+        <v>8016.13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1079454-1-CM26</t>
+          <t>707415-189-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2281,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>52363.31</v>
+        <v>438.25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>778992-12-CM26</t>
+          <t>778989-201-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2297,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2312,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>3a Briagada Acorazada "La Concepción"</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2342,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3929.99</v>
+        <v>16179.32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1057385-23-CM26</t>
+          <t>909389-30-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2358,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.980.580-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>Comité de Des Productivo Regional Antofagasta</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2403,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>21026.27</v>
+        <v>2945.33</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1077908-22-CM26</t>
+          <t>909389-31-SE25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2419,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2434,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.980.580-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>Comité de Des Productivo Regional Antofagasta</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2457,20 +2453,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>32767.77</v>
+        <v>61982.55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>707415-13-CM26</t>
+          <t>3506-940-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5519.68</v>
+        <v>3587.95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1057384-133-CM26</t>
+          <t>1079454-697-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2541,27 +2541,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>31579.3</v>
+        <v>1807.95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057385-46-CM26</t>
+          <t>1079454-702-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>19939.83</v>
+        <v>52379.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1079454-49-CM26</t>
+          <t>1383364-12-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2663,27 +2663,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.606.210-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>Servicio de Bienestar del Servicio Salud Antof</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1362.36</v>
+        <v>10025.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1077908-39-CM26</t>
+          <t>778992-376-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2724,27 +2724,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>36704.97</v>
+        <v>4403.35</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1057384-209-CM26</t>
+          <t>1410-2656-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>32808.91</v>
+        <v>165.58</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>881-36-CM26</t>
+          <t>1057385-570-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2864.09</v>
+        <v>12603.09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>707415-30-CM26</t>
+          <t>1077908-347-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2907,27 +2907,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2952,13 +2952,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>60020.08</v>
+        <v>35048.92</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>778998-5-CM26</t>
+          <t>1057384-4-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1705.61</v>
+        <v>30936.08</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1079454-54-CM26</t>
+          <t>1079454-1-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3029,17 +3029,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3074,13 +3074,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>45367.2</v>
+        <v>52363.31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1077908-58-CM26</t>
+          <t>778992-12-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>Regimiento Reforzado N° 1 "Calama"</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>35845.99</v>
+        <v>3929.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1057385-88-CM26</t>
+          <t>1077908-22-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3151,27 +3151,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>18389.07</v>
+        <v>32767.77</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4291-261-CM26</t>
+          <t>1057385-23-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3212,27 +3212,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3257,13 +3257,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8051.86</v>
+        <v>21026.27</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>778998-38-CM26</t>
+          <t>707415-13-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3273,27 +3273,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3318,13 +3318,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3280.31</v>
+        <v>5519.68</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1057384-301-CM26</t>
+          <t>1057384-133-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3334,17 +3334,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3379,13 +3379,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>34562.15</v>
+        <v>31579.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1220203-30-CM26</t>
+          <t>1057385-46-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3395,27 +3395,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3440,13 +3440,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>9014.299999999999</v>
+        <v>19939.83</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1079454-101-CM26</t>
+          <t>1079454-49-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>47072.65</v>
+        <v>1362.36</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1079454-102-CM26</t>
+          <t>1077908-39-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3517,27 +3517,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1413.8</v>
+        <v>36704.97</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1410-309-CM26</t>
+          <t>1057384-209-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>225.65</v>
+        <v>32808.91</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1079454-130-CM26</t>
+          <t>881-36-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>Gobierno Regional de Antofagasta</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>59066.6</v>
+        <v>2864.09</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1077908-81-CM26</t>
+          <t>707415-30-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3700,27 +3700,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>35207.21</v>
+        <v>60020.08</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1057385-126-CM26</t>
+          <t>778998-5-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>22264.88</v>
+        <v>1705.61</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2258-3406-CM26</t>
+          <t>1079454-54-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3822,27 +3822,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>48610.9</v>
+        <v>45367.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1057384-375-CM26</t>
+          <t>1077908-58-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>33109.57</v>
+        <v>35845.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>707415-64-CM26</t>
+          <t>1057385-88-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3944,27 +3944,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3989,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>607.29</v>
+        <v>18389.07</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>778998-80-CM26</t>
+          <t>4291-261-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4005,27 +4005,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>295.55</v>
+        <v>8051.86</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1079454-208-CM26</t>
+          <t>778998-38-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4111,13 +4111,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>62269.37</v>
+        <v>3280.31</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057385-156-CM26</t>
+          <t>1057384-301-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4127,27 +4127,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>13831.49</v>
+        <v>34562.15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1077908-101-CM26</t>
+          <t>1220203-30-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4188,27 +4188,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4233,13 +4233,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>37112.8</v>
+        <v>9014.299999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057384-464-CM26</t>
+          <t>1079454-101-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4294,28 +4294,28 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>35836.44</v>
+        <v>47072.65</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1057385-180-CM26</t>
+          <t>1079454-102-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4355,28 +4355,28 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>18065.3</v>
+        <v>1413.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1079454-294-CM26</t>
+          <t>1410-309-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4416,28 +4416,28 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>58517.82</v>
+        <v>225.65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1057384-568-CM26</t>
+          <t>1057385-126-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4477,43 +4477,43 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>37388.2</v>
+        <v>22264.88</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2122-152-CM26</t>
+          <t>1077908-81-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4538,43 +4538,43 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3279.74</v>
+        <v>35207.21</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1410-646-CM26</t>
+          <t>1079454-130-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>SECCIÓN COMPRAS II ZONA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4599,28 +4599,28 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>342.98</v>
+        <v>59066.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1410-645-CM26</t>
+          <t>2258-3406-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4660,43 +4660,43 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>160.77</v>
+        <v>48610.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>707415-87-CM26</t>
+          <t>1057384-375-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4721,28 +4721,28 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>583.09</v>
+        <v>33109.57</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1077908-137-CM26</t>
+          <t>707415-64-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4782,43 +4782,43 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3482.21</v>
+        <v>607.29</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4051-139-CM26</t>
+          <t>778998-80-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4843,33 +4843,33 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>11969.07</v>
+        <v>295.55</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1079454-324-CM26</t>
+          <t>1079454-208-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4904,33 +4904,33 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>58636.91</v>
+        <v>62269.37</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1057385-228-CM26</t>
+          <t>1057385-156-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4965,43 +4965,43 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>18854.82</v>
+        <v>13831.49</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4291-1122-CM26</t>
+          <t>1077908-101-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5026,43 +5026,43 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>8016.5</v>
+        <v>37112.8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>778998-131-CM26</t>
+          <t>1057384-464-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>355.46</v>
+        <v>35836.44</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2429-996-CM26</t>
+          <t>1057385-180-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5103,27 +5103,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5148,6 +5148,799 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
+        <v>18065.3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1079454-294-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>61.978.660-2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS II ZONA</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>58517.82</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1057384-568-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>61.606.203-4</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>37388.2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1410-645-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>61.004.007-1</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>160.77</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1410-646-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>61.004.007-1</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>342.98</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2122-152-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>3279.74</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>707415-87-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>583.09</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1077908-137-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>62.000.380-8</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>3482.21</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>4051-139-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>69.252.600-7</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>11969.07</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1079454-324-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>61.978.660-2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS II ZONA</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>58636.91</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1057385-228-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>61.606.204-2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>18854.82</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>4291-1122-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>8016.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>778998-131-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>61.964.800-5</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>355.46</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2429-996-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
         <v>32373.85</v>
       </c>
     </row>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/antofagasta.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M193"/>
+  <dimension ref="A1:M201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -656,7 +656,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1978,7 +1978,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3858-117-CM25</t>
+          <t>1410-369-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>35002.47</v>
+        <v>210.56</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1410-369-CM25</t>
+          <t>3858-117-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>210.56</v>
+        <v>35002.47</v>
       </c>
     </row>
     <row r="28">
@@ -2283,7 +2283,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1410-406-CM25</t>
+          <t>707415-37-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2303,17 +2303,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>202.23</v>
+        <v>4645.44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>707415-37-CM25</t>
+          <t>1410-406-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2364,17 +2364,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4645.44</v>
+        <v>202.23</v>
       </c>
     </row>
     <row r="33">
@@ -2649,7 +2649,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3506-309-CM25</t>
+          <t>2429-1896-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>994.87</v>
+        <v>29870.48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2429-1896-CM25</t>
+          <t>3506-309-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>29870.48</v>
+        <v>994.87</v>
       </c>
     </row>
     <row r="39">
@@ -2954,7 +2954,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3858-179-CM25</t>
+          <t>707415-50-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1460.94</v>
+        <v>371.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>707415-50-CM25</t>
+          <t>3858-178-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>371.2</v>
+        <v>121.74</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3858-178-CM25</t>
+          <t>3834-101-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>121.74</v>
+        <v>8896.74</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3834-101-CM25</t>
+          <t>3858-179-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>8896.74</v>
+        <v>1460.94</v>
       </c>
     </row>
     <row r="46">
@@ -3259,7 +3259,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>707415-53-CM25</t>
+          <t>922070-85-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3279,17 +3279,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.117.365-5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1123.19</v>
+        <v>1063.55</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>922070-85-CM25</t>
+          <t>707415-53-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>65.117.365-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1063.55</v>
+        <v>1123.19</v>
       </c>
     </row>
     <row r="49">
@@ -5577,7 +5577,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2429-2454-CM25</t>
+          <t>1013609-124-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5597,17 +5597,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>65.158.175-3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>25739.71</v>
+        <v>14555.44</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1013609-124-CM25</t>
+          <t>2429-2454-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5658,17 +5658,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>65.158.175-3</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>14555.44</v>
+        <v>25739.71</v>
       </c>
     </row>
     <row r="87">
@@ -6004,7 +6004,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4291-1656-CM25</t>
+          <t>1057385-367-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3100.84</v>
+        <v>19638.65</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1057385-367-CM25</t>
+          <t>4291-1656-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>19638.65</v>
+        <v>3100.84</v>
       </c>
     </row>
     <row r="94">
@@ -6492,7 +6492,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>769-4844-CM25</t>
+          <t>1077908-272-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>70741.96000000001</v>
+        <v>32648.72</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1077908-272-CM25</t>
+          <t>769-4844-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>32648.72</v>
+        <v>70741.96000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6736,7 +6736,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1079454-565-CM25</t>
+          <t>1079454-566-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>44863.33</v>
+        <v>1071.24</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1079454-566-CM25</t>
+          <t>1079454-565-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1071.24</v>
+        <v>44863.33</v>
       </c>
     </row>
     <row r="106">
@@ -6919,7 +6919,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>778992-318-CM25</t>
+          <t>778992-322-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3087.09</v>
+        <v>16547.97</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>778992-322-CM25</t>
+          <t>778992-318-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>16547.97</v>
+        <v>3087.09</v>
       </c>
     </row>
     <row r="109">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. Campo Militar "Antofagasta"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7956,7 +7956,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>778992-359-CM25</t>
+          <t>1079454-696-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>14978.91</v>
+        <v>39750.89</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1079454-696-CM25</t>
+          <t>778992-359-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>39750.89</v>
+        <v>14978.91</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1057384-882-CM25</t>
+          <t>4291-2855-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8098,17 +8098,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>29959.92</v>
+        <v>985.02</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4291-2855-CM25</t>
+          <t>1057384-882-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8159,17 +8159,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>985.02</v>
+        <v>29959.92</v>
       </c>
     </row>
     <row r="128">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8261,7 +8261,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>707415-189-CM25</t>
+          <t>3391-934-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8281,17 +8281,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>438.25</v>
+        <v>8016.13</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3391-934-CM25</t>
+          <t>707415-189-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8342,17 +8342,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>8016.13</v>
+        <v>438.25</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>778989-201-CM25</t>
+          <t>909389-30-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8403,17 +8403,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>61.980.580-1</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>16179.32</v>
+        <v>2945.33</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>909389-30-CM25</t>
+          <t>778989-201-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8464,17 +8464,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.980.580-1</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Comité de Des Productivo Regional Antofagasta</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2945.33</v>
+        <v>16179.32</v>
       </c>
     </row>
     <row r="133">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Comité de Des Productivo Regional Antofagasta</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8631,7 +8631,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1079454-702-CM25</t>
+          <t>1079454-697-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8686,13 +8686,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>52379.69</v>
+        <v>1807.95</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1079454-697-CM25</t>
+          <t>1079454-702-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1807.95</v>
+        <v>52379.69</v>
       </c>
     </row>
     <row r="137">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Servicio Salud Antof</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10522,7 +10522,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1057385-126-CM26</t>
+          <t>1079454-130-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10577,13 +10577,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>22264.88</v>
+        <v>59066.6</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1079454-130-CM26</t>
+          <t>1077908-81-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10638,13 +10638,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>59066.6</v>
+        <v>35207.21</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1077908-81-CM26</t>
+          <t>1057385-126-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>35207.21</v>
+        <v>22264.88</v>
       </c>
     </row>
     <row r="169">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11620,7 +11620,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1077908-137-CM26</t>
+          <t>4051-139-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11645,12 +11645,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11675,13 +11675,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3482.21</v>
+        <v>11969.07</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>4051-139-CM26</t>
+          <t>1077908-137-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11701,17 +11701,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>11969.07</v>
+        <v>3482.21</v>
       </c>
     </row>
     <row r="186">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -12225,6 +12225,494 @@
       </c>
       <c r="M193" s="2" t="n">
         <v>430.49</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1079454-394-CM26</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>61.978.660-2</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>52481.16</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>3274-212-CM26</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>10466.51</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>3506-682-CM26</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>7820.98</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1057384-737-CM26</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>61.606.203-4</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>34008.39</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1079454-409-CM26</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>61.978.660-2</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>2571.16</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1410-872-CM26</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>61.004.007-1</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>4072.98</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1057385-353-CM26</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>61.606.204-2</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>17365.2</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1079454-440-CM26</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>61.978.660-2</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>54935.84</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/antofagasta.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M201"/>
+  <dimension ref="A1:M203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1368,7 +1424,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1077908-44-CM25</t>
+          <t>1079454-78-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1388,17 +1444,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1416,20 +1472,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>32767.23</v>
+        <v>32440.18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1079454-78-CM25</t>
+          <t>1077908-44-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1449,17 +1509,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1477,14 +1537,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>32440.18</v>
+        <v>32767.23</v>
       </c>
     </row>
     <row r="18">
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1917,7 +2009,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1079454-130-CM25</t>
+          <t>3858-117-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,17 +2029,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1965,20 +2057,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1104.2</v>
+        <v>35002.47</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1410-369-CM25</t>
+          <t>1079454-130-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,17 +2094,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2026,20 +2122,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>210.56</v>
+        <v>1104.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3858-117-CM25</t>
+          <t>1410-369-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,12 +2164,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2087,14 +2187,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>35002.47</v>
+        <v>210.56</v>
       </c>
     </row>
     <row r="28">
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2161,7 +2269,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1220203-37-CM25</t>
+          <t>1057384-278-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2181,17 +2289,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2209,20 +2317,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>7921.97</v>
+        <v>27239.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1057384-278-CM25</t>
+          <t>1220203-37-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,17 +2354,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2270,14 +2382,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>27239.87</v>
+        <v>7921.97</v>
       </c>
     </row>
     <row r="31">
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3381,7 +3569,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3834-114-CM25</t>
+          <t>778992-139-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3406,12 +3594,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3429,20 +3617,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>6229.31</v>
+        <v>2406.78</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>778992-139-CM25</t>
+          <t>3834-114-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3467,12 +3659,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3490,14 +3682,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2406.78</v>
+        <v>6229.31</v>
       </c>
     </row>
     <row r="51">
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7224,7 +7664,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1057385-462-CM25</t>
+          <t>769-4874-SE25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,7 +7679,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,12 +7689,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7272,20 +7712,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>18124.58</v>
+        <v>959535.38</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1079454-606-CM25</t>
+          <t>1057385-462-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,7 +7744,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7310,12 +7754,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7333,20 +7777,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>52774.98</v>
+        <v>18124.58</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1077908-298-CM25</t>
+          <t>1079454-606-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,7 +7809,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7371,12 +7819,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7394,20 +7842,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>33059.44</v>
+        <v>52774.98</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1013609-152-CM25</t>
+          <t>1077908-298-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7417,12 +7869,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7884,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>65.158.175-3</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7455,20 +7907,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>21264.61</v>
+        <v>33059.44</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>778989-188-CM25</t>
+          <t>1013609-152-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,7 +7939,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7493,7 +7949,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>65.158.175-3</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7516,20 +7972,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>23003.57</v>
+        <v>21264.61</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>4291-2327-CM25</t>
+          <t>778989-188-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,22 +8004,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7577,20 +8037,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>4357.81</v>
+        <v>23003.57</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1057384-788-CM25</t>
+          <t>4291-2327-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,22 +8069,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7638,20 +8102,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>31016.26</v>
+        <v>4357.81</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3858-513-CM25</t>
+          <t>1057384-788-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,22 +8134,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7699,20 +8167,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>122.66</v>
+        <v>31016.26</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>778992-348-CM25</t>
+          <t>3858-513-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7727,22 +8199,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7760,20 +8232,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>5066.72</v>
+        <v>122.66</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1057385-515-CM25</t>
+          <t>778992-348-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7798,12 +8274,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7821,20 +8297,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>20222.02</v>
+        <v>5066.72</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1077908-325-CM25</t>
+          <t>1057385-515-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7849,22 +8329,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7882,20 +8362,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>33078.45</v>
+        <v>20222.02</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>697036-126-CM25</t>
+          <t>1077908-325-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7920,12 +8404,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7943,20 +8427,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>757.6900000000001</v>
+        <v>33078.45</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1079454-696-CM25</t>
+          <t>697036-126-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7966,27 +8454,27 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8004,20 +8492,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>39750.89</v>
+        <v>757.6900000000001</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>778992-359-CM25</t>
+          <t>1079454-696-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8042,12 +8534,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8065,20 +8557,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>14978.91</v>
+        <v>39750.89</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4291-2855-CM25</t>
+          <t>778992-359-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8093,22 +8589,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8126,20 +8622,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>985.02</v>
+        <v>14978.91</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1057384-882-CM25</t>
+          <t>4291-2855-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8159,17 +8659,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8187,20 +8687,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>29959.92</v>
+        <v>985.02</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>778998-192-CM25</t>
+          <t>1057384-882-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8225,12 +8729,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8248,20 +8752,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>6099.22</v>
+        <v>29959.92</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3391-934-CM25</t>
+          <t>778998-192-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8276,7 +8784,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8286,7 +8794,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -8309,20 +8817,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>8016.13</v>
+        <v>6099.22</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>707415-189-CM25</t>
+          <t>3391-934-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8342,17 +8854,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8370,20 +8882,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>438.25</v>
+        <v>8016.13</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>909389-30-CM25</t>
+          <t>707415-189-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8398,7 +8914,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8408,12 +8924,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.980.580-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8431,20 +8947,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2945.33</v>
+        <v>438.25</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>778989-201-CM25</t>
+          <t>909389-30-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8464,17 +8984,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>61.980.580-1</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8492,20 +9012,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>16179.32</v>
+        <v>2945.33</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>909389-31-SE25</t>
+          <t>778989-201-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8520,22 +9044,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.980.580-1</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8564,13 +9088,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>61982.55</v>
+        <v>16179.32</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3506-940-CM25</t>
+          <t>909389-31-SE25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8585,7 +9109,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8595,12 +9119,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.980.580-1</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8618,20 +9142,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3587.95</v>
+        <v>61982.55</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1079454-697-CM25</t>
+          <t>3506-940-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8646,7 +9174,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8656,12 +9184,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8679,20 +9207,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1807.95</v>
+        <v>3587.95</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1079454-702-CM25</t>
+          <t>1079454-697-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8712,7 +9244,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8740,20 +9272,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>52379.69</v>
+        <v>1807.95</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>778992-376-CM25</t>
+          <t>1079454-702-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8768,7 +9304,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8778,12 +9314,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8801,20 +9337,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>4403.35</v>
+        <v>52379.69</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1383364-12-CM25</t>
+          <t>778992-376-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8839,12 +9379,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.606.210-7</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8862,20 +9402,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>10025.38</v>
+        <v>4403.35</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1410-2656-CM25</t>
+          <t>1383364-12-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8890,7 +9434,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8900,12 +9444,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.210-7</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8923,20 +9467,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>165.58</v>
+        <v>10025.38</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1077908-347-CM25</t>
+          <t>1410-2656-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8961,12 +9509,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8984,20 +9532,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>35048.92</v>
+        <v>165.58</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1057385-570-CM25</t>
+          <t>1077908-347-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9022,12 +9574,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9045,20 +9597,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>12603.09</v>
+        <v>35048.92</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1057384-4-CM26</t>
+          <t>1057385-570-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9068,12 +9624,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9083,12 +9639,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9106,20 +9662,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>30936.08</v>
+        <v>12603.09</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1079454-1-CM26</t>
+          <t>1057384-4-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9134,22 +9694,22 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9167,20 +9727,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>52363.31</v>
+        <v>30936.08</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>778992-12-CM26</t>
+          <t>1079454-1-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9195,22 +9759,22 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9228,20 +9792,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3929.99</v>
+        <v>52363.31</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1057385-23-CM26</t>
+          <t>778992-12-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9256,7 +9824,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9266,12 +9834,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9289,20 +9857,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>21026.27</v>
+        <v>3929.99</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1077908-22-CM26</t>
+          <t>1057385-23-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9322,17 +9894,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9350,20 +9922,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>32767.77</v>
+        <v>21026.27</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>707415-13-CM26</t>
+          <t>1077908-22-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9373,12 +9949,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9388,12 +9964,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9411,20 +9987,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>5519.68</v>
+        <v>32767.77</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1057384-133-CM26</t>
+          <t>707415-13-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9439,22 +10019,22 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9472,20 +10052,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>31579.3</v>
+        <v>5519.68</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1057385-46-CM26</t>
+          <t>1057384-133-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9500,7 +10084,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9510,12 +10094,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9533,20 +10117,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>19939.83</v>
+        <v>31579.3</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1079454-49-CM26</t>
+          <t>1057385-46-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9561,22 +10149,22 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9594,20 +10182,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1362.36</v>
+        <v>19939.83</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1077908-39-CM26</t>
+          <t>1079454-49-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9632,12 +10224,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9655,20 +10247,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>36704.97</v>
+        <v>1362.36</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1057384-209-CM26</t>
+          <t>1077908-39-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9678,27 +10274,27 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9716,20 +10312,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>32808.91</v>
+        <v>36704.97</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>881-36-CM26</t>
+          <t>1057384-209-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9744,7 +10344,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9754,12 +10354,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9777,20 +10377,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2864.09</v>
+        <v>32808.91</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>707415-30-CM26</t>
+          <t>881-36-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9805,22 +10409,22 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9838,20 +10442,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>60020.08</v>
+        <v>2864.09</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>778998-5-CM26</t>
+          <t>707415-30-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9866,22 +10474,22 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9899,20 +10507,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1705.61</v>
+        <v>60020.08</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1079454-54-CM26</t>
+          <t>778998-5-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9927,7 +10539,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9937,12 +10549,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9960,20 +10572,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>45367.2</v>
+        <v>1705.61</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1077908-58-CM26</t>
+          <t>1079454-54-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9988,7 +10604,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9998,12 +10614,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10021,20 +10637,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>35845.99</v>
+        <v>45367.2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1057385-88-CM26</t>
+          <t>1077908-58-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10049,7 +10669,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10059,12 +10679,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10082,20 +10702,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>18389.07</v>
+        <v>35845.99</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4291-261-CM26</t>
+          <t>1057385-88-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10110,22 +10734,22 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10143,20 +10767,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>8051.86</v>
+        <v>18389.07</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>778998-38-CM26</t>
+          <t>4291-261-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10166,27 +10794,27 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10204,20 +10832,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3280.31</v>
+        <v>8051.86</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1057384-301-CM26</t>
+          <t>778998-38-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10232,22 +10864,22 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10265,20 +10897,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>34562.15</v>
+        <v>3280.31</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1220203-30-CM26</t>
+          <t>1057384-301-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10293,7 +10929,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10303,12 +10939,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10326,20 +10962,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>9014.299999999999</v>
+        <v>34562.15</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1079454-101-CM26</t>
+          <t>1220203-30-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10354,22 +10994,22 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10387,20 +11027,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>47072.65</v>
+        <v>9014.299999999999</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1079454-102-CM26</t>
+          <t>1079454-101-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10448,20 +11092,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1413.8</v>
+        <v>47072.65</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1410-309-CM26</t>
+          <t>1079454-102-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10476,7 +11124,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10486,12 +11134,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10509,20 +11157,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>225.65</v>
+        <v>1413.8</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1079454-130-CM26</t>
+          <t>1410-309-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10537,7 +11189,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10547,12 +11199,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10570,20 +11222,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>59066.6</v>
+        <v>225.65</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1077908-81-CM26</t>
+          <t>1079454-130-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10608,12 +11264,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10631,20 +11287,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>35207.21</v>
+        <v>59066.6</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1057385-126-CM26</t>
+          <t>1077908-81-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10669,12 +11329,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10692,20 +11352,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>22264.88</v>
+        <v>35207.21</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2258-3406-CM26</t>
+          <t>1057385-126-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10715,27 +11379,27 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10753,20 +11417,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>48610.9</v>
+        <v>22264.88</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1057384-375-CM26</t>
+          <t>2258-3406-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10781,22 +11449,22 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10814,20 +11482,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>33109.57</v>
+        <v>48610.9</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>707415-64-CM26</t>
+          <t>1057384-375-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10842,22 +11514,22 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10875,20 +11547,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>607.29</v>
+        <v>33109.57</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>778998-80-CM26</t>
+          <t>707415-64-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10903,22 +11579,22 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10936,20 +11612,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>295.55</v>
+        <v>607.29</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1079454-208-CM26</t>
+          <t>778998-80-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10964,7 +11644,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10974,12 +11654,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10997,20 +11677,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>62269.37</v>
+        <v>295.55</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1057385-156-CM26</t>
+          <t>1079454-208-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11035,12 +11719,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11058,20 +11742,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>13831.49</v>
+        <v>62269.37</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1077908-101-CM26</t>
+          <t>1057385-156-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11096,12 +11784,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11119,20 +11807,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>37112.8</v>
+        <v>13831.49</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1057384-464-CM26</t>
+          <t>1077908-101-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11142,12 +11834,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11157,12 +11849,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11180,35 +11872,39 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>35836.44</v>
+        <v>37112.8</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1057385-180-CM26</t>
+          <t>1057384-464-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11218,12 +11914,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11241,35 +11937,39 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>18065.3</v>
+        <v>35836.44</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1079454-294-CM26</t>
+          <t>1077908-117-SE26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11279,12 +11979,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11302,20 +12002,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>58517.82</v>
+        <v>445747.94</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1057384-568-CM26</t>
+          <t>1057385-180-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11330,7 +12034,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11340,12 +12044,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11363,20 +12067,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>37388.2</v>
+        <v>18065.3</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1410-645-CM26</t>
+          <t>1079454-294-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11391,22 +12099,22 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11416,28 +12124,32 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr"/>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>160.77</v>
+        <v>58517.82</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1410-646-CM26</t>
+          <t>1057384-568-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11452,22 +12164,22 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11477,28 +12189,32 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr"/>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>342.98</v>
+        <v>37388.2</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2122-152-CM26</t>
+          <t>1410-645-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11523,12 +12239,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11538,28 +12254,32 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr"/>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>3279.74</v>
+        <v>160.77</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>707415-87-CM26</t>
+          <t>1410-646-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11574,7 +12294,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11584,12 +12304,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11599,28 +12319,32 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr"/>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>583.09</v>
+        <v>342.98</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>4051-139-CM26</t>
+          <t>2122-152-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11635,7 +12359,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11645,12 +12369,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11668,20 +12392,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>11969.07</v>
+        <v>3279.74</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1077908-137-CM26</t>
+          <t>707415-87-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11696,22 +12424,22 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11729,20 +12457,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>3482.21</v>
+        <v>583.09</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1079454-324-CM26</t>
+          <t>4051-139-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11757,7 +12489,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11767,12 +12499,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11790,20 +12522,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>58636.91</v>
+        <v>11969.07</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1057385-228-CM26</t>
+          <t>1077908-137-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11818,22 +12554,22 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11851,20 +12587,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>18854.82</v>
+        <v>3482.21</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>4291-1122-CM26</t>
+          <t>1079454-324-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11889,12 +12629,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11912,20 +12652,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>8016.5</v>
+        <v>58636.91</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>778998-131-CM26</t>
+          <t>1057385-228-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11940,7 +12684,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11950,12 +12694,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11973,20 +12717,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>355.46</v>
+        <v>18854.82</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2429-996-CM26</t>
+          <t>4291-1122-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11996,12 +12744,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12011,12 +12759,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12026,28 +12774,32 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>32373.85</v>
+        <v>8016.5</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1057384-659-CM26</t>
+          <t>778998-131-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12057,27 +12809,27 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12095,20 +12847,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>34218.46</v>
+        <v>355.46</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1057385-285-CM26</t>
+          <t>2429-996-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12123,22 +12879,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12148,28 +12904,32 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>19594.7</v>
+        <v>32373.85</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>778989-161-CM26</t>
+          <t>1057384-659-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12184,7 +12944,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12194,12 +12954,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12217,20 +12977,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>430.49</v>
+        <v>34218.46</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1079454-394-CM26</t>
+          <t>1057385-285-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12240,12 +13004,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12255,12 +13019,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12278,20 +13042,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>52481.16</v>
+        <v>19594.7</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3274-212-CM26</t>
+          <t>778989-161-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12301,12 +13069,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -12316,12 +13084,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12331,28 +13099,32 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr"/>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>10466.51</v>
+        <v>430.49</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>3506-682-CM26</t>
+          <t>1079454-394-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12367,22 +13139,22 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12400,20 +13172,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>7820.98</v>
+        <v>52481.16</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1057384-737-CM26</t>
+          <t>3274-212-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12428,7 +13204,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12438,12 +13214,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12453,28 +13229,32 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr"/>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>34008.39</v>
+        <v>10466.51</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1079454-409-CM26</t>
+          <t>3506-682-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12489,22 +13269,22 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12522,20 +13302,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2571.16</v>
+        <v>7820.98</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1410-872-CM26</t>
+          <t>1057384-737-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12550,7 +13334,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12560,12 +13344,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12583,20 +13367,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>4072.98</v>
+        <v>34008.39</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1057385-353-CM26</t>
+          <t>1079454-409-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12611,22 +13399,22 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12644,74 +13432,212 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>17365.2</v>
+        <v>2571.16</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
+          <t>1410-872-CM26</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>61.004.007-1</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>4072.98</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1057385-353-CM26</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>61.606.204-2</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>17365.2</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
           <t>1079454-440-CM26</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B203" t="inlineStr">
         <is>
           <t>2239-1-LR26</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
+      <c r="C203" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="E203" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr">
+      <c r="F203" t="inlineStr">
         <is>
           <t>61.978.660-2</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
+      <c r="G203" t="inlineStr">
         <is>
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M201" s="2" t="n">
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="n">
         <v>54935.84</v>
       </c>
     </row>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/antofagasta.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M203"/>
+  <dimension ref="A1:M209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1424,7 +1424,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1079454-78-CM25</t>
+          <t>1077908-44-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>32440.18</v>
+        <v>32767.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1077908-44-CM25</t>
+          <t>1079454-78-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1509,17 +1509,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>32767.23</v>
+        <v>32440.18</v>
       </c>
     </row>
     <row r="18">
@@ -2009,7 +2009,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3858-117-CM25</t>
+          <t>1079454-130-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2029,17 +2029,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>35002.47</v>
+        <v>1104.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1079454-130-CM25</t>
+          <t>1410-369-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2094,17 +2094,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1104.2</v>
+        <v>210.56</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1410-369-CM25</t>
+          <t>3858-117-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>210.56</v>
+        <v>35002.47</v>
       </c>
     </row>
     <row r="28">
@@ -2269,7 +2269,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057384-278-CM25</t>
+          <t>1220203-37-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2289,17 +2289,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2328,13 +2328,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>27239.87</v>
+        <v>7921.97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1220203-37-CM25</t>
+          <t>1057384-278-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7921.97</v>
+        <v>27239.87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>707415-37-CM25</t>
+          <t>1410-406-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2419,17 +2419,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>4645.44</v>
+        <v>202.23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1410-406-CM25</t>
+          <t>707415-37-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2484,17 +2484,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>202.23</v>
+        <v>4645.44</v>
       </c>
     </row>
     <row r="33">
@@ -5649,7 +5649,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>769-4707-CM25</t>
+          <t>1077908-182-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>69524.67999999999</v>
+        <v>29370.98</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1077908-182-CM25</t>
+          <t>769-4707-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>29370.98</v>
+        <v>69524.67999999999</v>
       </c>
     </row>
     <row r="83">
@@ -6364,7 +6364,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1057385-367-CM25</t>
+          <t>4291-1656-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6384,17 +6384,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6423,13 +6423,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>19638.65</v>
+        <v>3100.84</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4291-1656-CM25</t>
+          <t>1057385-367-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6449,17 +6449,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3100.84</v>
+        <v>19638.65</v>
       </c>
     </row>
     <row r="94">
@@ -6884,7 +6884,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1077908-272-CM25</t>
+          <t>769-4844-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>32648.72</v>
+        <v>70741.96000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>769-4844-CM25</t>
+          <t>1077908-272-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6974,12 +6974,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>70741.96000000001</v>
+        <v>32648.72</v>
       </c>
     </row>
     <row r="102">
@@ -7144,7 +7144,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1079454-566-CM25</t>
+          <t>1079454-565-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7203,13 +7203,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1071.24</v>
+        <v>44863.33</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1079454-565-CM25</t>
+          <t>1079454-566-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>44863.33</v>
+        <v>1071.24</v>
       </c>
     </row>
     <row r="106">
@@ -8509,7 +8509,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1079454-696-CM25</t>
+          <t>778992-359-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8568,13 +8568,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>39750.89</v>
+        <v>14978.91</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>778992-359-CM25</t>
+          <t>1079454-696-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>14978.91</v>
+        <v>39750.89</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4291-2855-CM25</t>
+          <t>1057384-882-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8659,17 +8659,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8698,13 +8698,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>985.02</v>
+        <v>29959.92</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1057384-882-CM25</t>
+          <t>778998-192-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.964.800-5</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8763,13 +8763,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>29959.92</v>
+        <v>6099.22</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>778998-192-CM25</t>
+          <t>4291-2855-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8789,17 +8789,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.964.800-5</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>6099.22</v>
+        <v>985.02</v>
       </c>
     </row>
     <row r="130">
@@ -9549,7 +9549,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1077908-347-CM25</t>
+          <t>1057385-570-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9608,13 +9608,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>35048.92</v>
+        <v>12603.09</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1057385-570-CM25</t>
+          <t>1077908-347-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>12603.09</v>
+        <v>35048.92</v>
       </c>
     </row>
     <row r="143">
@@ -10199,7 +10199,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1079454-49-CM26</t>
+          <t>1077908-39-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10258,13 +10258,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1362.36</v>
+        <v>36704.97</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1077908-39-CM26</t>
+          <t>1079454-49-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10323,7 +10323,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>36704.97</v>
+        <v>1362.36</v>
       </c>
     </row>
     <row r="153">
@@ -11694,7 +11694,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1079454-208-CM26</t>
+          <t>1077908-101-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>62269.37</v>
+        <v>37112.8</v>
       </c>
     </row>
     <row r="175">
@@ -11824,7 +11824,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1077908-101-CM26</t>
+          <t>1079454-208-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11849,12 +11849,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11883,7 +11883,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>37112.8</v>
+        <v>62269.37</v>
       </c>
     </row>
     <row r="177">
@@ -12604,7 +12604,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1079454-324-CM26</t>
+          <t>1057385-228-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12663,13 +12663,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>58636.91</v>
+        <v>18854.82</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1057385-228-CM26</t>
+          <t>4291-1122-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12694,12 +12694,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12728,13 +12728,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>18854.82</v>
+        <v>8016.5</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>4291-1122-CM26</t>
+          <t>1079454-324-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>8016.5</v>
+        <v>58636.91</v>
       </c>
     </row>
     <row r="191">
@@ -13599,7 +13599,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -13639,6 +13639,396 @@
       </c>
       <c r="M203" s="2" t="n">
         <v>54935.84</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>769-672-CM26</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>61.606.200-k</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>941166.91</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>3506-752-CM26</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>2055.2</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1057384-806-CM26</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>61.606.203-4</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="n">
+        <v>32233.32</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>3506-777-CM26</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>1147.6</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>3506-778-CM26</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="n">
+        <v>19372.14</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>896-38-CM26</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="n">
+        <v>4425.41</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/antofagasta.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/antofagasta.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/antofagasta.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M209"/>
+  <dimension ref="A1:M212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2399,7 +2399,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1410-406-CM25</t>
+          <t>707415-37-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2419,17 +2419,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>202.23</v>
+        <v>4645.44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>707415-37-CM25</t>
+          <t>1410-406-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2484,17 +2484,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4645.44</v>
+        <v>202.23</v>
       </c>
     </row>
     <row r="33">
@@ -3959,7 +3959,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1079454-224-CM25</t>
+          <t>1077908-96-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3979,17 +3979,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>47374.84</v>
+        <v>33056.45</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1077908-96-CM25</t>
+          <t>1079454-224-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4044,17 +4044,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>33056.45</v>
+        <v>47374.84</v>
       </c>
     </row>
     <row r="57">
@@ -4869,7 +4869,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3845-36-CM25</t>
+          <t>1057385-267-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4889,17 +4889,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4928,13 +4928,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>11639.91</v>
+        <v>20304.79</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1057385-267-CM25</t>
+          <t>3845-36-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4954,17 +4954,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>20304.79</v>
+        <v>11639.91</v>
       </c>
     </row>
     <row r="71">
@@ -5649,7 +5649,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1077908-182-CM25</t>
+          <t>769-4707-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>29370.98</v>
+        <v>69524.67999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>769-4707-CM25</t>
+          <t>1077908-182-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>69524.67999999999</v>
+        <v>29370.98</v>
       </c>
     </row>
     <row r="83">
@@ -6884,7 +6884,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>769-4844-CM25</t>
+          <t>1077908-272-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6943,13 +6943,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>70741.96000000001</v>
+        <v>32648.72</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1077908-272-CM25</t>
+          <t>769-4844-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6974,12 +6974,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>32648.72</v>
+        <v>70741.96000000001</v>
       </c>
     </row>
     <row r="102">
@@ -7144,7 +7144,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1079454-565-CM25</t>
+          <t>1079454-566-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7203,13 +7203,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>44863.33</v>
+        <v>1071.24</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1079454-566-CM25</t>
+          <t>1079454-565-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1071.24</v>
+        <v>44863.33</v>
       </c>
     </row>
     <row r="106">
@@ -8249,7 +8249,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>778992-348-CM25</t>
+          <t>1057385-515-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8308,13 +8308,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>5066.72</v>
+        <v>20222.02</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1057385-515-CM25</t>
+          <t>778992-348-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>20222.02</v>
+        <v>5066.72</v>
       </c>
     </row>
     <row r="123">
@@ -8509,7 +8509,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>778992-359-CM25</t>
+          <t>1079454-696-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.953.000-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8568,13 +8568,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>14978.91</v>
+        <v>39750.89</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1079454-696-CM25</t>
+          <t>778992-359-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.953.000-4</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>39750.89</v>
+        <v>14978.91</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1057384-882-CM25</t>
+          <t>4291-2855-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8659,17 +8659,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8698,7 +8698,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>29959.92</v>
+        <v>985.02</v>
       </c>
     </row>
     <row r="128">
@@ -8769,7 +8769,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4291-2855-CM25</t>
+          <t>1057384-882-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8789,17 +8789,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8828,7 +8828,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>985.02</v>
+        <v>29959.92</v>
       </c>
     </row>
     <row r="130">
@@ -11044,7 +11044,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1079454-101-CM26</t>
+          <t>1079454-102-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11103,13 +11103,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>47072.65</v>
+        <v>1413.8</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1079454-102-CM26</t>
+          <t>1079454-101-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11168,7 +11168,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1413.8</v>
+        <v>47072.65</v>
       </c>
     </row>
     <row r="166">
@@ -11239,7 +11239,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1079454-130-CM26</t>
+          <t>1077908-81-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11298,13 +11298,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>59066.6</v>
+        <v>35207.21</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1077908-81-CM26</t>
+          <t>1057385-126-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11329,12 +11329,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11363,13 +11363,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>35207.21</v>
+        <v>22264.88</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1057385-126-CM26</t>
+          <t>1079454-130-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>22264.88</v>
+        <v>59066.6</v>
       </c>
     </row>
     <row r="170">
@@ -11694,7 +11694,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1077908-101-CM26</t>
+          <t>1057385-156-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11753,13 +11753,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>37112.8</v>
+        <v>13831.49</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1057385-156-CM26</t>
+          <t>1079454-208-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11818,13 +11818,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>13831.49</v>
+        <v>62269.37</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1079454-208-CM26</t>
+          <t>1077908-101-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11849,12 +11849,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11883,7 +11883,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>62269.37</v>
+        <v>37112.8</v>
       </c>
     </row>
     <row r="177">
@@ -12214,7 +12214,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1410-645-CM26</t>
+          <t>2122-152-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12239,12 +12239,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -12273,7 +12273,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>160.77</v>
+        <v>3279.74</v>
       </c>
     </row>
     <row r="183">
@@ -12344,7 +12344,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2122-152-CM26</t>
+          <t>1410-645-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12384,12 +12384,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3279.74</v>
+        <v>160.77</v>
       </c>
     </row>
     <row r="185">
@@ -12604,7 +12604,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1057385-228-CM26</t>
+          <t>1079454-324-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12663,13 +12663,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>18854.82</v>
+        <v>58636.91</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>4291-1122-CM26</t>
+          <t>1057385-228-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12689,17 +12689,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12728,13 +12728,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>8016.5</v>
+        <v>18854.82</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1079454-324-CM26</t>
+          <t>4291-1122-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12754,17 +12754,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12793,7 +12793,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>58636.91</v>
+        <v>8016.5</v>
       </c>
     </row>
     <row r="191">
@@ -13124,7 +13124,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1079454-394-CM26</t>
+          <t>3274-212-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -13164,12 +13164,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -13183,13 +13183,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>52481.16</v>
+        <v>10466.51</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3274-212-CM26</t>
+          <t>1079454-394-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13214,12 +13214,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13229,12 +13229,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13248,7 +13248,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>10466.51</v>
+        <v>52481.16</v>
       </c>
     </row>
     <row r="198">
@@ -14029,6 +14029,201 @@
       </c>
       <c r="M209" s="2" t="n">
         <v>4425.41</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>1604-161-CM26</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>60.511.020-7</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="n">
+        <v>547.35</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1079454-478-CM26</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>61.978.660-2</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="n">
+        <v>1327.09</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>1604-162-CM26</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>60.511.020-7</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="n">
+        <v>668.98</v>
       </c>
     </row>
   </sheetData>
